--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__SEND MXL.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__SEND MXL.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC15"/>
+  <dimension ref="A1:AC25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,12 +578,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>347412</t>
+          <t>72905</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>89577</t>
+          <t>70723</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -593,17 +593,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>DAYRANN</t>
+          <t>YESSIKA ANABEL</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>FIERRO</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -613,10 +613,14 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>6242385160</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>6863997069</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>CENISO 4111</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -624,22 +628,22 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>14-11-2010</t>
+          <t>18-02-2022</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>NOTIENE2026@GMAIL.COM</t>
+          <t>YEKA_RZF@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>02-03-2026 07:11:45</t>
+          <t>14-02-2022 19:08:58</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -649,28 +653,28 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>02-03-2026 07:13:01</t>
+          <t>03-03-2026 18:32:08</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V2" t="inlineStr"/>
@@ -681,36 +685,36 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>26010522781730005290</t>
+          <t>26010522855430005552</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Javier Galaz Quintero</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>347512</t>
+          <t>346834</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>89677</t>
+          <t>88999</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -720,17 +724,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>MARIAN ARLYN</t>
+          <t>JUAN GILBERTO</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>LABRADA</t>
+          <t>CAZARES</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>OLVERA</t>
+          <t>ESCARREGA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -740,7 +744,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6861636687</t>
+          <t>6863039245</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -751,22 +755,22 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>17-03-2006</t>
+          <t>21-06-1994</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>ARLYNOLVERA@GMAIL.COM</t>
+          <t>GILBERTOCAZARES2@GMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>02-03-2026 11:45:41</t>
+          <t>26-02-2026 21:05:12</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -776,17 +780,17 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>02-03-2026 11:47:18</t>
+          <t>02-03-2026 22:56:47</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -808,14 +812,22 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26010522789680005337</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
+          <t>26010522821240005454</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>CHRISTIAN ERNESTO QUIÑONES GALVEZ</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -832,12 +844,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>347507</t>
+          <t>249633</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>89672</t>
+          <t>47137</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -847,17 +859,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SANDRA LUZ</t>
+          <t>JESUS MARIANO</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ARBALLO</t>
+          <t>SÁNCHEZ</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>RICO</t>
+          <t>GARIBALDI</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -867,67 +879,79 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6863454718</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>6971047744</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ZSDFG</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>22-04-1988</t>
+          <t>01-12-2003</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>SANDYLUZAR@HOTMAIL.COM</t>
+          <t>SANCHEZGARIBALDIJ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>02-03-2026 11:25:27</t>
+          <t>01-08-2024 19:07:46</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>02-03-2026 11:28:15</t>
+          <t>03-03-2026 16:17:33</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr"/>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>03-03-2026 16:14:24</t>
+        </is>
+      </c>
       <c r="U4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr"/>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W4" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -935,14 +959,18 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26010522789210005336</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr"/>
+          <t>26010522846200005529</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1106,12 +1134,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>346834</t>
+          <t>347093</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>88999</t>
+          <t>89258</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1121,17 +1149,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>JUAN GILBERTO</t>
+          <t xml:space="preserve">ARTURO </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CAZARES</t>
+          <t>HINOJOSA</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ESCARREGA</t>
+          <t>FIERRO</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1141,67 +1169,79 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6863039245</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>6867221281</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>DFB</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>21-06-1994</t>
+          <t>28-02-1996</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>GILBERTOCAZARES2@GMAIL.COM</t>
+          <t>AHINOJOS809@GMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>26-02-2026 21:05:12</t>
+          <t>27-02-2026 20:53:44</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>02-03-2026 22:56:47</t>
+          <t>03-03-2026 19:27:54</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr"/>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>03-03-2026 19:27:21</t>
+        </is>
+      </c>
       <c r="U6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr"/>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W6" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1209,7 +1249,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26010522821240005454</t>
+          <t>26010522858800005570</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1224,7 +1264,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1372,12 +1412,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>347870</t>
+          <t>347412</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>90035</t>
+          <t>89577</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1387,17 +1427,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>FRANCISCO JOSUE</t>
+          <t>DAYRANN</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FERNANDEZ</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>BECERRA</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1407,7 +1447,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6643747758</t>
+          <t>6242385160</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1418,22 +1458,22 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>12-02-1997</t>
+          <t>14-11-2010</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>JOSUE.FERNANDEZ@UABC.EDU.MX</t>
+          <t>NOTIENE2026@GMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>02-03-2026 19:32:25</t>
+          <t>02-03-2026 07:11:45</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1443,17 +1483,17 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>02-03-2026 19:33:13</t>
+          <t>02-03-2026 07:13:01</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1464,7 +1504,7 @@
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V8" t="inlineStr"/>
@@ -1475,36 +1515,36 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26010522817050005414</t>
+          <t>26010522781730005290</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Javier Galaz Quintero</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>347454</t>
+          <t>121844</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>89619</t>
+          <t>19537</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1514,17 +1554,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ERIDT PALOMO</t>
+          <t xml:space="preserve">VIANEY </t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ORTEGA</t>
+          <t xml:space="preserve">MONTEVERDE </t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>BARRIGA</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1534,28 +1574,32 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6863647203</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>6863363547</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>DE LOS CAROLES 1881</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>13-02-2002</t>
+          <t>08-08-2006</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>ERIDTORTEGA966@GMAIL.COM</t>
+          <t>MONTEVERDE@GMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>02-03-2026 08:46:21</t>
+          <t>10-09-2022 12:01:14</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1580,12 +1624,12 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>02-03-2026 08:48:24</t>
+          <t>03-03-2026 11:22:51</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T9" t="inlineStr"/>
@@ -1602,11 +1646,19 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26010522784770005313</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
+          <t>26010522837400005504</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>NORMA VERONICA MEJIA MACIAS</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>549</t>
@@ -1626,12 +1678,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>347475</t>
+          <t>347507</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>89640</t>
+          <t>89672</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1641,17 +1693,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">GRECIA MIRANDA </t>
+          <t>SANDRA LUZ</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARTINEZ </t>
+          <t>ARBALLO</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>JAUREGUI</t>
+          <t>RICO</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1661,7 +1713,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6531372814</t>
+          <t>6863454718</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1672,22 +1724,22 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>15-07-2007</t>
+          <t>22-04-1988</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>GRECIA.MARTINEZ.JAUREGUI@UABC.EDU.MX</t>
+          <t>SANDYLUZAR@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>02-03-2026 09:57:27</t>
+          <t>02-03-2026 11:25:27</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1697,17 +1749,17 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>02-03-2026 10:06:24</t>
+          <t>02-03-2026 11:28:15</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1729,36 +1781,36 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26010522787130005326</t>
+          <t>26010522789210005336</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Cristobal Lopez Miranda</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>347868</t>
+          <t>347454</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>90033</t>
+          <t>89619</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1768,17 +1820,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>JOSE GUADALUPE</t>
+          <t>ERIDT PALOMO</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">CAMPOS </t>
+          <t>ORTEGA</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>BARRIGA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1788,47 +1840,43 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6864620686</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>CVB</t>
-        </is>
-      </c>
+          <t>6863647203</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>24-05-1998</t>
+          <t>13-02-2002</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>SKRET48@GMAIL.COM</t>
+          <t>ERIDTORTEGA966@GMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>02-03-2026 19:28:28</t>
+          <t>02-03-2026 08:46:21</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -1838,7 +1886,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>02-03-2026 19:30:20</t>
+          <t>02-03-2026 08:48:24</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1846,21 +1894,13 @@
           <t>02-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>02-03-2026 19:29:47</t>
-        </is>
-      </c>
+      <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1868,7 +1908,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26010522816900005412</t>
+          <t>26010522784770005313</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr"/>
@@ -1892,12 +1932,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>347856</t>
+          <t>347475</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>90021</t>
+          <t>89640</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1907,17 +1947,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">VICTOR MOISES </t>
+          <t xml:space="preserve">GRECIA MIRANDA </t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>LEON</t>
+          <t xml:space="preserve">MARTINEZ </t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CIPRIAN</t>
+          <t>JAUREGUI</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1927,47 +1967,43 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6862806630</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>CERRO LORETO 524</t>
-        </is>
-      </c>
+          <t>6531372814</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>14-07-2006</t>
+          <t>15-07-2007</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>ANNASTACIA841@GMAIL.COM</t>
+          <t>GRECIA.MARTINEZ.JAUREGUI@UABC.EDU.MX</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>02-03-2026 18:56:42</t>
+          <t>02-03-2026 09:57:27</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -1977,7 +2013,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>02-03-2026 18:59:57</t>
+          <t>02-03-2026 10:06:24</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1985,21 +2021,13 @@
           <t>02-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>02-03-2026 18:59:18</t>
-        </is>
-      </c>
+      <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2007,7 +2035,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26010522814900005394</t>
+          <t>26010522787130005326</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr"/>
@@ -2019,24 +2047,24 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Cristobal Lopez Miranda</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>347866</t>
+          <t>347512</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>90031</t>
+          <t>89677</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2046,17 +2074,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>MARIA FERNANDA</t>
+          <t>MARIAN ARLYN</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>IBARRA</t>
+          <t>LABRADA</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>OLVERA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2066,14 +2094,10 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6864247889</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>XFGHSRT</t>
-        </is>
-      </c>
+          <t>6861636687</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -2081,32 +2105,32 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>24-01-2000</t>
+          <t>17-03-2006</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>FERNANDADEBI@GMAIL.COM</t>
+          <t>ARLYNOLVERA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>02-03-2026 19:23:59</t>
+          <t>02-03-2026 11:45:41</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -2116,7 +2140,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>02-03-2026 19:27:24</t>
+          <t>02-03-2026 11:47:18</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -2124,21 +2148,13 @@
           <t>02-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>02-03-2026 19:26:48</t>
-        </is>
-      </c>
+      <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2146,7 +2162,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26010522816660005411</t>
+          <t>26010522789680005337</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr"/>
@@ -2170,12 +2186,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>347801</t>
+          <t>347870</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>89966</t>
+          <t>90035</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2185,17 +2201,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">JUAN IGNACIO </t>
+          <t>FRANCISCO JOSUE</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">PADILLA </t>
+          <t>FERNANDEZ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>BECERRA</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2205,57 +2221,53 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6863540077</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>VALLE OJOS NEGROS 757</t>
-        </is>
-      </c>
+          <t>6643747758</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>18-05-2000</t>
+          <t>12-02-1997</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>JUANIGNACIOPADILLAHERNANDEZ@GMAIL.COM</t>
+          <t>JOSUE.FERNANDEZ@UABC.EDU.MX</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>02-03-2026 18:13:39</t>
+          <t>02-03-2026 19:32:25</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>02-03-2026 18:26:08</t>
+          <t>02-03-2026 19:33:13</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -2263,21 +2275,13 @@
           <t>02-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>02-03-2026 18:23:34</t>
-        </is>
-      </c>
+      <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2285,14 +2289,14 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26010522811900005387</t>
+          <t>26010522817050005414</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -2309,12 +2313,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>347862</t>
+          <t>347931</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>90027</t>
+          <t>90096</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2324,17 +2328,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>DAVID ALEJANDRO</t>
+          <t>DIEGO IVAN</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CIPRIAN</t>
+          <t>GODOY</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>BELTRAN</t>
+          <t>VELEZQUEZ</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2344,14 +2348,10 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6863468966</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>CERRO LORETO 524</t>
-        </is>
-      </c>
+          <t>6863853422</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -2359,32 +2359,32 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>26-10-1996</t>
+          <t>27-01-2006</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>ALEXDUTY@GMAIL.COM</t>
+          <t>DGODOY.I.827@GMAIL.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>02-03-2026 19:12:02</t>
+          <t>03-03-2026 05:04:50</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -2394,29 +2394,21 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>02-03-2026 19:14:31</t>
+          <t>03-03-2026 05:08:27</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>02-03-2026 19:13:58</t>
-        </is>
-      </c>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2424,7 +2416,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26010522815760005403</t>
+          <t>26010522822770005455</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr"/>
@@ -2440,6 +2432,1376 @@
         </is>
       </c>
       <c r="AC15" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>347801</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>89966</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JUAN IGNACIO </t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PADILLA </t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>6863540077</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>VALLE OJOS NEGROS 757</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>18-05-2000</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>JUANIGNACIOPADILLAHERNANDEZ@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>02-03-2026 18:13:39</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>02-03-2026 18:26:08</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>02-03-2026 18:23:34</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>26010522811900005387</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>347862</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>90027</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>DAVID ALEJANDRO</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>CIPRIAN</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>BELTRAN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>6863468966</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>CERRO LORETO 524</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>26-10-1996</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>ALEXDUTY@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>02-03-2026 19:12:02</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>02-03-2026 19:14:31</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>02-03-2026 19:13:58</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>26010522815760005403</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>347868</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>90033</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>JOSE GUADALUPE</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CAMPOS </t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>FLORES</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>6864620686</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>CVB</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>24-05-1998</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>SKRET48@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>02-03-2026 19:28:28</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>02-03-2026 19:30:20</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>02-03-2026 19:29:47</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>26010522816900005412</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>347984</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>90149</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>DANIELA</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>VELASCO</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>MARTINEZ</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>6862443184</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>23-07-2003</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>VELASCO.DANIELA@UABC.EDU.MX</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>03-03-2026 09:14:52</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>03-03-2026 09:17:36</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>26010522834610005488</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>348294</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>90459</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MIRANDA </t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CARRAZCO </t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>MEZA</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>6863919464</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>DFB</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>29-11-2006</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>MIRANDACARRAZCO1@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>03-03-2026 21:19:57</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>03-03-2026 21:22:26</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>03-03-2026 21:21:59</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>26010522862110005602</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>348106</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>90271</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>JULIO CESAR</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SANCHEZ </t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>GARIBALDI</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>6971153889</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ASC</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>28-06-2000</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>JULIOCSANCHEZGARI@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>03-03-2026 16:04:08</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>03-03-2026 16:08:28</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>03-03-2026 16:07:31</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>26010522845650005525</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>348250</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>90415</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>FRIDA GABRIELA</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NEVAREZ </t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>ARANGURE</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>6863950637</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>FERMIN RIVERA 1501</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>29-09-1999</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>FRIDARANGURE@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>03-03-2026 19:00:45</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>03-03-2026 19:45:30</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>26010522859740005576</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>348267</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>90432</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADOLFO ANGEL </t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ALVARADO </t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>ALVAREZ</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>6381141056</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>GUIRNALDA 991</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>02-08-1999</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>ALVARADOADOLFO07@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>03-03-2026 19:26:50</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>03-03-2026 19:32:17</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>03-03-2026 19:31:29</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>26010522859120005572</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>347856</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>90021</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VICTOR MOISES </t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>LEON</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>CIPRIAN</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>6862806630</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>CERRO LORETO 524</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>14-07-2006</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>ANNASTACIA841@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>02-03-2026 18:56:42</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>02-03-2026 18:59:57</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>02-03-2026 18:59:18</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>26010522814900005394</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>347866</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>90031</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>MARIA FERNANDA</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>IBARRA</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>LOPEZ</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>6864247889</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>XFGHSRT</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>24-01-2000</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>FERNANDADEBI@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>02-03-2026 19:23:59</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>02-03-2026 19:27:24</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>02-03-2026 19:26:48</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>26010522816660005411</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
         <is>
           <t>sin rutina</t>
         </is>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__SEND MXL.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__SEND MXL.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC25"/>
+  <dimension ref="A1:AC36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -709,12 +709,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>346834</t>
+          <t>249633</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>88999</t>
+          <t>47137</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -724,17 +724,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>JUAN GILBERTO</t>
+          <t>JESUS MARIANO</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CAZARES</t>
+          <t>SÁNCHEZ</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ESCARREGA</t>
+          <t>GARIBALDI</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -744,67 +744,79 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6863039245</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>6971047744</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ZSDFG</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>21-06-1994</t>
+          <t>01-12-2003</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>GILBERTOCAZARES2@GMAIL.COM</t>
+          <t>SANCHEZGARIBALDIJ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>26-02-2026 21:05:12</t>
+          <t>01-08-2024 19:07:46</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>02-03-2026 22:56:47</t>
+          <t>03-03-2026 16:17:33</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr"/>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>03-03-2026 16:14:24</t>
+        </is>
+      </c>
       <c r="U3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr"/>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W3" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -812,22 +824,18 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26010522821240005454</t>
+          <t>26010522846200005529</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>CHRISTIAN ERNESTO QUIÑONES GALVEZ</t>
-        </is>
-      </c>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -844,12 +852,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>249633</t>
+          <t>261646</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>47137</t>
+          <t>59150</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -859,17 +867,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>JESUS MARIANO</t>
+          <t>VICTOR ALEXANDER</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>SÁNCHEZ</t>
+          <t>QUINTANA</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>GARIBALDI</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -879,14 +887,10 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6971047744</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>ZSDFG</t>
-        </is>
-      </c>
+          <t>6624295211</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -894,32 +898,32 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>01-12-2003</t>
+          <t>08-02-1988</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>SANCHEZGARIBALDIJ@GMAIL.COM</t>
+          <t>QUINTANAVICTOR@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>01-08-2024 19:07:46</t>
+          <t>11-10-2024 21:33:35</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -929,29 +933,21 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>03-03-2026 16:17:33</t>
+          <t>04-03-2026 15:40:17</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>03-03-2026 16:14:24</t>
-        </is>
-      </c>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -959,14 +955,10 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26010522846200005529</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26010522885580005673</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr">
         <is>
@@ -975,12 +967,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Eduardo  Rivera Ramirez</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
@@ -1134,12 +1126,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>347093</t>
+          <t>114183</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>89258</t>
+          <t>11912</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1149,17 +1141,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARTURO </t>
+          <t>CECCILIA</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>HINOJOSA</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>FIERRO</t>
+          <t>GARIBAY</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1169,79 +1161,71 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6867221281</t>
+          <t>6862020008</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>DFB</t>
+          <t>CARCATINESIS 348</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>28-02-1996</t>
+          <t>23-11-1974</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>AHINOJOS809@GMAIL.COM</t>
+          <t>CEXYGTE@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>27-02-2026 20:53:44</t>
+          <t>08-08-2022 11:01:34</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>03-03-2026 19:27:54</t>
+          <t>02-03-2026 08:34:20</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>03-03-2026 19:27:21</t>
-        </is>
-      </c>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1249,22 +1233,14 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26010522858800005570</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>CHRISTIAN ERNESTO QUIÑONES GALVEZ</t>
-        </is>
-      </c>
+          <t>26010522784250005307</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1281,12 +1257,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>114183</t>
+          <t>199152</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>11912</t>
+          <t>96659</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1296,17 +1272,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CECCILIA</t>
+          <t xml:space="preserve">MARIA ANTONIETA </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>GARIBAY</t>
+          <t>OLGUIN</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1316,14 +1292,10 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6862020008</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>CARCATINESIS 348</t>
-        </is>
-      </c>
+          <t>6862112403</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -1331,17 +1303,17 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>23-11-1974</t>
+          <t>13-06-1979</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>CEXYGTE@HOTMAIL.COM</t>
+          <t>CONNYPERZOLGUIN@GMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>08-08-2022 11:01:34</t>
+          <t>27-09-2023 06:26:26</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1366,12 +1338,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>02-03-2026 08:34:20</t>
+          <t>05-03-2026 10:04:50</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>05-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
@@ -1388,7 +1360,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26010522784250005307</t>
+          <t>26010522912390005769</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr"/>
@@ -1412,12 +1384,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>347412</t>
+          <t>346834</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>89577</t>
+          <t>88999</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1427,17 +1399,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>DAYRANN</t>
+          <t>JUAN GILBERTO</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>CAZARES</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>ESCARREGA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1447,7 +1419,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6242385160</t>
+          <t>6863039245</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1458,22 +1430,22 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>14-11-2010</t>
+          <t>21-06-1994</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>NOTIENE2026@GMAIL.COM</t>
+          <t>GILBERTOCAZARES2@GMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>02-03-2026 07:11:45</t>
+          <t>26-02-2026 21:05:12</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1483,17 +1455,17 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>02-03-2026 07:13:01</t>
+          <t>02-03-2026 22:56:47</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1504,7 +1476,7 @@
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V8" t="inlineStr"/>
@@ -1515,24 +1487,32 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26010522781730005290</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
+          <t>26010522821240005454</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>CHRISTIAN ERNESTO QUIÑONES GALVEZ</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Javier Galaz Quintero</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
@@ -1678,12 +1658,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>347507</t>
+          <t>347396</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>89672</t>
+          <t>89561</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1693,17 +1673,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>SANDRA LUZ</t>
+          <t>ARELY</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ARBALLO</t>
+          <t xml:space="preserve">RAMOS </t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>RICO</t>
+          <t>NUÑEZ</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1713,10 +1693,14 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6863454718</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>6865305780</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -1724,56 +1708,64 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>22-04-1988</t>
+          <t>14-04-2000</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>SANDYLUZAR@HOTMAIL.COM</t>
+          <t>ARELYRAMOS1960@GMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>02-03-2026 11:25:27</t>
+          <t>02-03-2026 06:00:12</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>02-03-2026 11:28:15</t>
+          <t>04-03-2026 05:21:09</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr"/>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>03-03-2026 11:30:09</t>
+        </is>
+      </c>
       <c r="U10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr"/>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W10" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1781,36 +1773,44 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26010522789210005336</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
+          <t>26010522864510005614</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>NORMA VERONICA MEJIA MACIAS</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Cristobal Lopez Miranda</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>347454</t>
+          <t>347507</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>89619</t>
+          <t>89672</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1820,17 +1820,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ERIDT PALOMO</t>
+          <t>SANDRA LUZ</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ORTEGA</t>
+          <t>ARBALLO</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>BARRIGA</t>
+          <t>RICO</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1840,33 +1840,33 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6863647203</t>
+          <t>6863454718</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>13-02-2002</t>
+          <t>22-04-1988</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>ERIDTORTEGA966@GMAIL.COM</t>
+          <t>SANDYLUZAR@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>02-03-2026 08:46:21</t>
+          <t>02-03-2026 11:25:27</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1876,17 +1876,17 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>02-03-2026 08:48:24</t>
+          <t>02-03-2026 11:28:15</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1908,14 +1908,14 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26010522784770005313</t>
+          <t>26010522789210005336</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -1932,12 +1932,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>347475</t>
+          <t>347454</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>89640</t>
+          <t>89619</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1947,17 +1947,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">GRECIA MIRANDA </t>
+          <t>ERIDT PALOMO</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARTINEZ </t>
+          <t>ORTEGA</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>JAUREGUI</t>
+          <t>BARRIGA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1967,28 +1967,28 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6531372814</t>
+          <t>6863647203</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>15-07-2007</t>
+          <t>13-02-2002</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>GRECIA.MARTINEZ.JAUREGUI@UABC.EDU.MX</t>
+          <t>ERIDTORTEGA966@GMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>02-03-2026 09:57:27</t>
+          <t>02-03-2026 08:46:21</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>02-03-2026 10:06:24</t>
+          <t>02-03-2026 08:48:24</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26010522787130005326</t>
+          <t>26010522784770005313</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr"/>
@@ -2047,24 +2047,24 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Cristobal Lopez Miranda</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>347512</t>
+          <t>347475</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>89677</t>
+          <t>89640</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2074,17 +2074,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>MARIAN ARLYN</t>
+          <t xml:space="preserve">GRECIA MIRANDA </t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>LABRADA</t>
+          <t xml:space="preserve">MARTINEZ </t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>OLVERA</t>
+          <t>JAUREGUI</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2094,7 +2094,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6861636687</t>
+          <t>6531372814</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2105,17 +2105,17 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>17-03-2006</t>
+          <t>15-07-2007</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>ARLYNOLVERA@GMAIL.COM</t>
+          <t>GRECIA.MARTINEZ.JAUREGUI@UABC.EDU.MX</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>02-03-2026 11:45:41</t>
+          <t>02-03-2026 09:57:27</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2140,7 +2140,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>02-03-2026 11:47:18</t>
+          <t>02-03-2026 10:06:24</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26010522789680005337</t>
+          <t>26010522787130005326</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr"/>
@@ -2174,24 +2174,24 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Cristobal Lopez Miranda</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>347870</t>
+          <t>347343</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>90035</t>
+          <t>89508</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2201,17 +2201,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>FRANCISCO JOSUE</t>
+          <t>CARLOS ABISAI</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>FERNANDEZ</t>
+          <t>BELTRÁN</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>BECERRA</t>
+          <t>ESTRADA</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2221,33 +2221,29 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6643747758</t>
+          <t>6861349523</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Femenino</t>
-        </is>
-      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>12-02-1997</t>
+          <t>04-11-2002</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>JOSUE.FERNANDEZ@UABC.EDU.MX</t>
+          <t>ANISAYESTRADA04@GMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>02-03-2026 19:32:25</t>
+          <t>01-03-2026 12:49:26</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -2257,22 +2253,22 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>02-03-2026 19:33:13</t>
+          <t>04-03-2026 05:42:16</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>04-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T14" t="inlineStr"/>
@@ -2289,14 +2285,18 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26010522817050005414</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr"/>
+          <t>26010522865050005622</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -2313,12 +2313,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>347931</t>
+          <t>347870</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>90096</t>
+          <t>90035</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2328,17 +2328,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>DIEGO IVAN</t>
+          <t>FRANCISCO JOSUE</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>GODOY</t>
+          <t>FERNANDEZ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>VELEZQUEZ</t>
+          <t>BECERRA</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2348,33 +2348,33 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6863853422</t>
+          <t>6643747758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>27-01-2006</t>
+          <t>12-02-1997</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>DGODOY.I.827@GMAIL.COM</t>
+          <t>JOSUE.FERNANDEZ@UABC.EDU.MX</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>03-03-2026 05:04:50</t>
+          <t>02-03-2026 19:32:25</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -2384,22 +2384,22 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>03-03-2026 05:08:27</t>
+          <t>02-03-2026 19:33:13</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T15" t="inlineStr"/>
@@ -2416,14 +2416,14 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26010522822770005455</t>
+          <t>26010522817050005414</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -2440,12 +2440,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>347801</t>
+          <t>347931</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>89966</t>
+          <t>90096</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2455,17 +2455,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">JUAN IGNACIO </t>
+          <t>DIEGO IVAN</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">PADILLA </t>
+          <t>GODOY</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>VELEZQUEZ</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2475,14 +2475,10 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6863540077</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>VALLE OJOS NEGROS 757</t>
-        </is>
-      </c>
+          <t>6863853422</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -2490,32 +2486,32 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>18-05-2000</t>
+          <t>27-01-2006</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>JUANIGNACIOPADILLAHERNANDEZ@GMAIL.COM</t>
+          <t>DGODOY.I.827@GMAIL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>02-03-2026 18:13:39</t>
+          <t>03-03-2026 05:04:50</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -2525,29 +2521,21 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>02-03-2026 18:26:08</t>
+          <t>03-03-2026 05:08:27</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>02-03-2026 18:23:34</t>
-        </is>
-      </c>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2555,7 +2543,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26010522811900005387</t>
+          <t>26010522822770005455</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr"/>
@@ -2579,12 +2567,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>347862</t>
+          <t>347412</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>90027</t>
+          <t>89577</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2594,17 +2582,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>DAVID ALEJANDRO</t>
+          <t>DAYRANN</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CIPRIAN</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>BELTRAN</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2614,47 +2602,43 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6863468966</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>CERRO LORETO 524</t>
-        </is>
-      </c>
+          <t>6242385160</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>26-10-1996</t>
+          <t>14-11-2010</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>ALEXDUTY@GMAIL.COM</t>
+          <t>NOTIENE2026@GMAIL.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>02-03-2026 19:12:02</t>
+          <t>02-03-2026 07:11:45</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -2664,7 +2648,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>02-03-2026 19:14:31</t>
+          <t>02-03-2026 07:13:01</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2672,21 +2656,13 @@
           <t>02-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>02-03-2026 19:13:58</t>
-        </is>
-      </c>
+      <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2694,7 +2670,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26010522815760005403</t>
+          <t>26010522781730005290</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr"/>
@@ -2706,24 +2682,24 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Javier Galaz Quintero</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>347868</t>
+          <t>347512</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>90033</t>
+          <t>89677</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2733,17 +2709,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>JOSE GUADALUPE</t>
+          <t>MARIAN ARLYN</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">CAMPOS </t>
+          <t>LABRADA</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>OLVERA</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2753,14 +2729,10 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6864620686</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>CVB</t>
-        </is>
-      </c>
+          <t>6861636687</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -2768,32 +2740,32 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>24-05-1998</t>
+          <t>17-03-2006</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>SKRET48@GMAIL.COM</t>
+          <t>ARLYNOLVERA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>02-03-2026 19:28:28</t>
+          <t>02-03-2026 11:45:41</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -2803,7 +2775,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>02-03-2026 19:30:20</t>
+          <t>02-03-2026 11:47:18</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2811,21 +2783,13 @@
           <t>02-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>02-03-2026 19:29:47</t>
-        </is>
-      </c>
+      <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2833,7 +2797,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26010522816900005412</t>
+          <t>26010522789680005337</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr"/>
@@ -2857,12 +2821,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>347984</t>
+          <t>347399</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>90149</t>
+          <t>89564</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2872,17 +2836,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>DANIELA</t>
+          <t>PEDRO</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>VELASCO</t>
+          <t>SANTIAGO</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>ORGANISTA</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2892,43 +2856,47 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>6862443184</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>6864336712</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>23-07-2003</t>
+          <t>07-10-1995</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>VELASCO.DANIELA@UABC.EDU.MX</t>
+          <t>PEDRO_SANTIAGO95@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>03-03-2026 09:14:52</t>
+          <t>02-03-2026 06:08:22</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -2938,7 +2906,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>03-03-2026 09:17:36</t>
+          <t>05-03-2026 06:20:12</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2946,13 +2914,21 @@
           <t>03-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr"/>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>02-03-2026 06:16:21</t>
+        </is>
+      </c>
       <c r="U19" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr"/>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W19" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2960,11 +2936,19 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26010522834610005488</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr"/>
-      <c r="Z19" t="inlineStr"/>
+          <t>26010522908290005745</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>NORMA VERONICA MEJIA MACIAS</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>549</t>
@@ -3123,12 +3107,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>348106</t>
+          <t>347868</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>90271</t>
+          <t>90033</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3138,17 +3122,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>JULIO CESAR</t>
+          <t>JOSE GUADALUPE</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">SANCHEZ </t>
+          <t xml:space="preserve">CAMPOS </t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>GARIBALDI</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3158,32 +3142,32 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>6971153889</t>
+          <t>6864620686</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>CVB</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>28-06-2000</t>
+          <t>24-05-1998</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>JULIOCSANCHEZGARI@GMAIL.COM</t>
+          <t>SKRET48@GMAIL.COM</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>03-03-2026 16:04:08</t>
+          <t>02-03-2026 19:28:28</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -3208,17 +3192,17 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>03-03-2026 16:08:28</t>
+          <t>02-03-2026 19:30:20</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>03-03-2026 16:07:31</t>
+          <t>02-03-2026 19:29:47</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -3238,7 +3222,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26010522845650005525</t>
+          <t>26010522816900005412</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr"/>
@@ -3262,12 +3246,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>348250</t>
+          <t>347984</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>90415</t>
+          <t>90149</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3277,17 +3261,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>FRIDA GABRIELA</t>
+          <t>DANIELA</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">NEVAREZ </t>
+          <t>VELASCO</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>ARANGURE</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3297,14 +3281,10 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>6863950637</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>FERMIN RIVERA 1501</t>
-        </is>
-      </c>
+          <t>6862443184</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -3312,17 +3292,17 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>29-09-1999</t>
+          <t>23-07-2003</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>FRIDARANGURE@GMAIL.COM</t>
+          <t>VELASCO.DANIELA@UABC.EDU.MX</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>03-03-2026 19:00:45</t>
+          <t>03-03-2026 09:14:52</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -3347,7 +3327,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>03-03-2026 19:45:30</t>
+          <t>03-03-2026 09:17:36</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -3369,7 +3349,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>26010522859740005576</t>
+          <t>26010522834610005488</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr"/>
@@ -3393,12 +3373,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>348267</t>
+          <t>348106</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>90432</t>
+          <t>90271</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3408,17 +3388,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADOLFO ANGEL </t>
+          <t>JULIO CESAR</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALVARADO </t>
+          <t xml:space="preserve">SANCHEZ </t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ALVAREZ</t>
+          <t>GARIBALDI</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3428,12 +3408,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>6381141056</t>
+          <t>6971153889</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>GUIRNALDA 991</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3443,17 +3423,17 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>02-08-1999</t>
+          <t>28-06-2000</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>ALVARADOADOLFO07@GMAIL.COM</t>
+          <t>JULIOCSANCHEZGARI@GMAIL.COM</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>03-03-2026 19:26:50</t>
+          <t>03-03-2026 16:04:08</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -3478,7 +3458,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>03-03-2026 19:32:17</t>
+          <t>03-03-2026 16:08:28</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -3488,7 +3468,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>03-03-2026 19:31:29</t>
+          <t>03-03-2026 16:07:31</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -3498,7 +3478,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
@@ -3508,7 +3488,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>26010522859120005572</t>
+          <t>26010522845650005525</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr"/>
@@ -3532,12 +3512,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>347856</t>
+          <t>347801</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>90021</t>
+          <t>89966</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3547,17 +3527,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">VICTOR MOISES </t>
+          <t xml:space="preserve">JUAN IGNACIO </t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>LEON</t>
+          <t xml:space="preserve">PADILLA </t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CIPRIAN</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3567,12 +3547,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>6862806630</t>
+          <t>6863540077</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>CERRO LORETO 524</t>
+          <t>VALLE OJOS NEGROS 757</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3582,17 +3562,17 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>14-07-2006</t>
+          <t>18-05-2000</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>ANNASTACIA841@GMAIL.COM</t>
+          <t>JUANIGNACIOPADILLAHERNANDEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>02-03-2026 18:56:42</t>
+          <t>02-03-2026 18:13:39</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3617,7 +3597,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>02-03-2026 18:59:57</t>
+          <t>02-03-2026 18:26:08</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3627,7 +3607,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>02-03-2026 18:59:18</t>
+          <t>02-03-2026 18:23:34</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3647,7 +3627,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>26010522814900005394</t>
+          <t>26010522811900005387</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr"/>
@@ -3659,24 +3639,24 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Eduardo  Rivera Ramirez</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>347866</t>
+          <t>347862</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>90031</t>
+          <t>90027</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3686,17 +3666,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>MARIA FERNANDA</t>
+          <t>DAVID ALEJANDRO</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>IBARRA</t>
+          <t>CIPRIAN</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>BELTRAN</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3706,32 +3686,32 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>6864247889</t>
+          <t>6863468966</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>XFGHSRT</t>
+          <t>CERRO LORETO 524</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>24-01-2000</t>
+          <t>26-10-1996</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>FERNANDADEBI@GMAIL.COM</t>
+          <t>ALEXDUTY@GMAIL.COM</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>02-03-2026 19:23:59</t>
+          <t>02-03-2026 19:12:02</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3756,7 +3736,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>02-03-2026 19:27:24</t>
+          <t>02-03-2026 19:14:31</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3766,7 +3746,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>02-03-2026 19:26:48</t>
+          <t>02-03-2026 19:13:58</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3786,7 +3766,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>26010522816660005411</t>
+          <t>26010522815760005403</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr"/>
@@ -3802,6 +3782,1499 @@
         </is>
       </c>
       <c r="AC25" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>347856</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>90021</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VICTOR MOISES </t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>LEON</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>CIPRIAN</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>6862806630</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>CERRO LORETO 524</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>14-07-2006</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>ANNASTACIA841@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>02-03-2026 18:56:42</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>02-03-2026 18:59:57</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>02-03-2026 18:59:18</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>26010522814900005394</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>347866</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>90031</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>MARIA FERNANDA</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>IBARRA</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>LOPEZ</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>6864247889</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>XFGHSRT</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>24-01-2000</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>FERNANDADEBI@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>02-03-2026 19:23:59</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>02-03-2026 19:27:24</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>02-03-2026 19:26:48</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>26010522816660005411</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>347093</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>89258</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARTURO </t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>HINOJOSA</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>FIERRO</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>6867221281</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>DFB</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>28-02-1996</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>AHINOJOS809@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>27-02-2026 20:53:44</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>03-03-2026 19:27:54</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>03-03-2026 19:27:21</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>26010522858800005570</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>CHRISTIAN ERNESTO QUIÑONES GALVEZ</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>347365</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>89530</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>ARJENNIS</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>FIERRO</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>ORTEGA</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>6864599242</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>28-11-2002</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>ARJENNIS.FIERRO28@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>02-03-2026 00:25:45</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>04-03-2026 05:42:50</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>26010522865080005623</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>348267</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>90432</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADOLFO ANGEL </t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ALVARADO </t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>ALVAREZ</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>6381141056</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>GUIRNALDA 991</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>02-08-1999</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>ALVARADOADOLFO07@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>03-03-2026 19:26:50</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>03-03-2026 19:32:17</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>03-03-2026 19:31:29</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>26010522859120005572</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>348250</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>90415</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>FRIDA GABRIELA</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NEVAREZ </t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>ARANGURE</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>6863950637</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>FERMIN RIVERA 1501</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>29-09-1999</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>FRIDARANGURE@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>03-03-2026 19:00:45</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>03-03-2026 19:45:30</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>26010522859740005576</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>348740</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>90905</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>DIANA ELIZABETH</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>FERNANDEZ</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>ROBLES</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>6861377114</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>FDGH</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>14-01-1976</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>DIANAFERNANDEZ1401@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>05-03-2026 16:13:04</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>05-03-2026 16:17:39</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>05-03-2026 16:17:02</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>26010522920680005786</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>348789</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>90954</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DULCE KARINA </t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SANDOVAL </t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>GUTIERREZ</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>6862476066</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>03-07-1995</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>KARISAN030795@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>05-03-2026 18:11:01</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>05-03-2026 18:23:48</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>26010522926990005795</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>348326</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>90491</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KEYLA </t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>SANCHEZ</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>RAMIREZ</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>6861631127</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>23-11-2012</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>NOTIENCORREO@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>04-03-2026 07:02:53</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>04-03-2026 07:05:18</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>26010522873570005627</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>Javier Galaz Quintero</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>348803</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>90968</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>JESUS ALBERTO</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>MENDIVIL</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>VALENZUELA</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>6442612015</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>FSFDG</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>15-11-1997</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>JAMV.MVJA@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>05-03-2026 19:26:51</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>05-03-2026 19:33:05</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>05-03-2026 19:32:23</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>26010522929680005806</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>348807</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>90972</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>ITATY ARLETT</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>VALDEZ</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>ANGUIS</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>6862318833</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>DZFG</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>24-08-2000</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>NOTELECTRCORR@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>05-03-2026 19:35:31</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>05-03-2026 19:38:30</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>05-03-2026 19:37:55</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>26010522929930005807</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
         <is>
           <t>sin rutina</t>
         </is>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__SEND MXL.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__SEND MXL.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC36"/>
+  <dimension ref="A1:AC38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,12 +578,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>72905</t>
+          <t>121844</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>70723</t>
+          <t>19537</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -593,17 +593,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>YESSIKA ANABEL</t>
+          <t xml:space="preserve">VIANEY </t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t xml:space="preserve">MONTEVERDE </t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>FIERRO</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -613,12 +613,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>6863997069</t>
+          <t>6863363547</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>CENISO 4111</t>
+          <t>DE LOS CAROLES 1881</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -628,22 +628,22 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>18-02-2022</t>
+          <t>08-08-2006</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>YEKA_RZF@HOTMAIL.COM</t>
+          <t>MONTEVERDE@GMAIL.COM</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>14-02-2022 19:08:58</t>
+          <t>10-09-2022 12:01:14</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -653,22 +653,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>03-03-2026 18:32:08</t>
+          <t>03-03-2026 11:22:51</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T2" t="inlineStr"/>
@@ -685,14 +685,22 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>26010522855430005552</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
+          <t>26010522837400005504</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>NORMA VERONICA MEJIA MACIAS</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -709,12 +717,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>249633</t>
+          <t>346834</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>47137</t>
+          <t>88999</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -724,17 +732,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>JESUS MARIANO</t>
+          <t>JUAN GILBERTO</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>SÁNCHEZ</t>
+          <t>CAZARES</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>GARIBALDI</t>
+          <t>ESCARREGA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -744,79 +752,67 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6971047744</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>ZSDFG</t>
-        </is>
-      </c>
+          <t>6863039245</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>01-12-2003</t>
+          <t>21-06-1994</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>SANCHEZGARIBALDIJ@GMAIL.COM</t>
+          <t>GILBERTOCAZARES2@GMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>01-08-2024 19:07:46</t>
+          <t>26-02-2026 21:05:12</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>03-03-2026 16:17:33</t>
+          <t>02-03-2026 22:56:47</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>03-03-2026 16:14:24</t>
-        </is>
-      </c>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -824,18 +820,22 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26010522846200005529</t>
+          <t>26010522821240005454</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr"/>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>CHRISTIAN ERNESTO QUIÑONES GALVEZ</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -852,12 +852,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>261646</t>
+          <t>114183</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>59150</t>
+          <t>11912</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -867,17 +867,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VICTOR ALEXANDER</t>
+          <t>CECCILIA</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>QUINTANA</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>GARIBAY</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -887,33 +887,37 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6624295211</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>6862020008</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>CARCATINESIS 348</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>08-02-1988</t>
+          <t>23-11-1974</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>QUINTANAVICTOR@HOTMAIL.COM</t>
+          <t>CEXYGTE@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>11-10-2024 21:33:35</t>
+          <t>08-08-2022 11:01:34</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -923,22 +927,22 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>04-03-2026 15:40:17</t>
+          <t>02-03-2026 08:34:20</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
@@ -955,36 +959,36 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26010522885580005673</t>
+          <t>26010522784250005307</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Eduardo  Rivera Ramirez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>346585</t>
+          <t>199152</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>88750</t>
+          <t>96659</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -994,17 +998,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>BETSY</t>
+          <t xml:space="preserve">MARIA ANTONIETA </t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">MORALES </t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUIJADA </t>
+          <t>OLGUIN</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1014,14 +1018,10 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6863893330</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>BRIONS 585</t>
-        </is>
-      </c>
+          <t>6862112403</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -1029,64 +1029,56 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>18-10-2008</t>
+          <t>13-06-1979</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>BETSYMORALEES@GMAIL.COM</t>
+          <t>CONNYPERZOLGUIN@GMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>25-02-2026 19:18:01</t>
+          <t>27-09-2023 06:26:26</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>02-03-2026 21:26:46</t>
+          <t>05-03-2026 10:04:50</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>02-03-2026 21:25:54</t>
-        </is>
-      </c>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1094,22 +1086,14 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26010522820850005449</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>CHRISTIAN ERNESTO QUIÑONES GALVEZ</t>
-        </is>
-      </c>
+          <t>26010522912390005769</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1126,12 +1110,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>114183</t>
+          <t>72905</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>11912</t>
+          <t>70723</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1141,17 +1125,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CECCILIA</t>
+          <t>YESSIKA ANABEL</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>GARIBAY</t>
+          <t>FIERRO</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1161,12 +1145,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6862020008</t>
+          <t>6863997069</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CARCATINESIS 348</t>
+          <t>CENISO 4111</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1176,17 +1160,17 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>23-11-1974</t>
+          <t>18-02-2022</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>CEXYGTE@HOTMAIL.COM</t>
+          <t>YEKA_RZF@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>08-08-2022 11:01:34</t>
+          <t>14-02-2022 19:08:58</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1211,7 +1195,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>02-03-2026 08:34:20</t>
+          <t>03-03-2026 18:32:08</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1233,7 +1217,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26010522784250005307</t>
+          <t>26010522855430005552</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr"/>
@@ -1257,12 +1241,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>199152</t>
+          <t>347093</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>96659</t>
+          <t>89258</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1272,17 +1256,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARIA ANTONIETA </t>
+          <t xml:space="preserve">ARTURO </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>HINOJOSA</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>OLGUIN</t>
+          <t>FIERRO</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1292,67 +1276,79 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6862112403</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>6867221281</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>DFB</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>13-06-1979</t>
+          <t>28-02-1996</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>CONNYPERZOLGUIN@GMAIL.COM</t>
+          <t>AHINOJOS809@GMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>27-09-2023 06:26:26</t>
+          <t>27-02-2026 20:53:44</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>05-03-2026 10:04:50</t>
+          <t>03-03-2026 19:27:54</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>05-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr"/>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>03-03-2026 19:27:21</t>
+        </is>
+      </c>
       <c r="U7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr"/>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W7" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1360,14 +1356,22 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26010522912390005769</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
+          <t>26010522858800005570</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>CHRISTIAN ERNESTO QUIÑONES GALVEZ</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -1384,12 +1388,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>346834</t>
+          <t>347365</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>88999</t>
+          <t>89530</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1399,17 +1403,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>JUAN GILBERTO</t>
+          <t>ARJENNIS</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CAZARES</t>
+          <t>FIERRO</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ESCARREGA</t>
+          <t>ORTEGA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1419,33 +1423,29 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6863039245</t>
+          <t>6864599242</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Femenino</t>
-        </is>
-      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>21-06-1994</t>
+          <t>28-11-2002</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>GILBERTOCAZARES2@GMAIL.COM</t>
+          <t>ARJENNIS.FIERRO28@GMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>26-02-2026 21:05:12</t>
+          <t>02-03-2026 00:25:45</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1455,22 +1455,22 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>02-03-2026 22:56:47</t>
+          <t>04-03-2026 05:42:50</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T8" t="inlineStr"/>
@@ -1487,22 +1487,18 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26010522821240005454</t>
+          <t>26010522865080005623</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>CHRISTIAN ERNESTO QUIÑONES GALVEZ</t>
-        </is>
-      </c>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -1519,12 +1515,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>121844</t>
+          <t>347343</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>19537</t>
+          <t>89508</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1534,17 +1530,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIANEY </t>
+          <t>CARLOS ABISAI</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">MONTEVERDE </t>
+          <t>BELTRÁN</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>ESTRADA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1554,32 +1550,24 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6863363547</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>DE LOS CAROLES 1881</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Femenino</t>
-        </is>
-      </c>
+          <t>6861349523</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>08-08-2006</t>
+          <t>04-11-2002</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>MONTEVERDE@GMAIL.COM</t>
+          <t>ANISAYESTRADA04@GMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>10-09-2022 12:01:14</t>
+          <t>01-03-2026 12:49:26</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1604,7 +1592,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>03-03-2026 11:22:51</t>
+          <t>04-03-2026 05:42:16</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1626,19 +1614,15 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26010522837400005504</t>
+          <t>26010522865050005622</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>NORMA VERONICA MEJIA MACIAS</t>
-        </is>
-      </c>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr">
         <is>
           <t>549</t>
@@ -1658,12 +1642,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>347396</t>
+          <t>347399</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>89561</t>
+          <t>89564</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1673,17 +1657,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ARELY</t>
+          <t>PEDRO</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">RAMOS </t>
+          <t>SANTIAGO</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>NUÑEZ</t>
+          <t>ORGANISTA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1693,7 +1677,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6865305780</t>
+          <t>6864336712</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1703,27 +1687,27 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>14-04-2000</t>
+          <t>07-10-1995</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>ARELYRAMOS1960@GMAIL.COM</t>
+          <t>PEDRO_SANTIAGO95@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>02-03-2026 06:00:12</t>
+          <t>02-03-2026 06:08:22</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1733,7 +1717,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1743,17 +1727,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>04-03-2026 05:21:09</t>
+          <t>05-03-2026 06:20:12</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>03-03-2026 11:30:09</t>
+          <t>02-03-2026 06:16:21</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1773,7 +1757,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26010522864510005614</t>
+          <t>26010522908290005745</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1793,24 +1777,24 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Cristobal Lopez Miranda</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>347507</t>
+          <t>347454</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>89672</t>
+          <t>89619</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1820,17 +1804,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>SANDRA LUZ</t>
+          <t>ERIDT PALOMO</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ARBALLO</t>
+          <t>ORTEGA</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>RICO</t>
+          <t>BARRIGA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1840,33 +1824,33 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6863454718</t>
+          <t>6863647203</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>22-04-1988</t>
+          <t>13-02-2002</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>SANDYLUZAR@HOTMAIL.COM</t>
+          <t>ERIDTORTEGA966@GMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>02-03-2026 11:25:27</t>
+          <t>02-03-2026 08:46:21</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1876,22 +1860,22 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>02-03-2026 11:28:15</t>
+          <t>02-03-2026 08:48:24</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T11" t="inlineStr"/>
@@ -1908,14 +1892,14 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26010522789210005336</t>
+          <t>26010522784770005313</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -1932,12 +1916,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>347454</t>
+          <t>347475</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>89619</t>
+          <t>89640</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1947,17 +1931,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ERIDT PALOMO</t>
+          <t xml:space="preserve">GRECIA MIRANDA </t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ORTEGA</t>
+          <t xml:space="preserve">MARTINEZ </t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>BARRIGA</t>
+          <t>JAUREGUI</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1967,28 +1951,28 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6863647203</t>
+          <t>6531372814</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>13-02-2002</t>
+          <t>15-07-2007</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>ERIDTORTEGA966@GMAIL.COM</t>
+          <t>GRECIA.MARTINEZ.JAUREGUI@UABC.EDU.MX</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>02-03-2026 08:46:21</t>
+          <t>02-03-2026 09:57:27</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -2013,12 +1997,12 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>02-03-2026 08:48:24</t>
+          <t>02-03-2026 10:06:24</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T12" t="inlineStr"/>
@@ -2035,7 +2019,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26010522784770005313</t>
+          <t>26010522787130005326</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr"/>
@@ -2047,24 +2031,24 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Cristobal Lopez Miranda</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>347475</t>
+          <t>347412</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>89640</t>
+          <t>89577</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2074,17 +2058,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">GRECIA MIRANDA </t>
+          <t>DAYRANN</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARTINEZ </t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>JAUREGUI</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2094,7 +2078,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6531372814</t>
+          <t>6242385160</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2105,17 +2089,17 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>15-07-2007</t>
+          <t>14-11-2010</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>GRECIA.MARTINEZ.JAUREGUI@UABC.EDU.MX</t>
+          <t>NOTIENE2026@GMAIL.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>02-03-2026 09:57:27</t>
+          <t>02-03-2026 07:11:45</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2140,18 +2124,18 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>02-03-2026 10:06:24</t>
+          <t>02-03-2026 07:13:01</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V13" t="inlineStr"/>
@@ -2162,7 +2146,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26010522787130005326</t>
+          <t>26010522781730005290</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr"/>
@@ -2174,7 +2158,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Cristobal Lopez Miranda</t>
+          <t>Javier Galaz Quintero</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2186,12 +2170,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>347343</t>
+          <t>347507</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>89508</t>
+          <t>89672</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2201,17 +2185,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>CARLOS ABISAI</t>
+          <t>SANDRA LUZ</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>BELTRÁN</t>
+          <t>ARBALLO</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ESTRADA</t>
+          <t>RICO</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2221,29 +2205,33 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6861349523</t>
+          <t>6863454718</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>04-11-2002</t>
+          <t>22-04-1988</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>ANISAYESTRADA04@GMAIL.COM</t>
+          <t>SANDYLUZAR@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>01-03-2026 12:49:26</t>
+          <t>02-03-2026 11:25:27</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -2253,22 +2241,22 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>04-03-2026 05:42:16</t>
+          <t>02-03-2026 11:28:15</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T14" t="inlineStr"/>
@@ -2285,18 +2273,14 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26010522865050005622</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26010522789210005336</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -2313,12 +2297,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>347870</t>
+          <t>249633</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>90035</t>
+          <t>47137</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2328,17 +2312,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>FRANCISCO JOSUE</t>
+          <t>JESUS MARIANO</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>FERNANDEZ</t>
+          <t>SÁNCHEZ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>BECERRA</t>
+          <t>GARIBALDI</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2348,53 +2332,57 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6643747758</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>6971047744</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ZSDFG</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>12-02-1997</t>
+          <t>01-12-2003</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>JOSUE.FERNANDEZ@UABC.EDU.MX</t>
+          <t>SANCHEZGARIBALDIJ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>02-03-2026 19:32:25</t>
+          <t>01-08-2024 19:07:46</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>02-03-2026 19:33:13</t>
+          <t>03-03-2026 16:17:33</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2402,13 +2390,21 @@
           <t>02-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr"/>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>03-03-2026 16:14:24</t>
+        </is>
+      </c>
       <c r="U15" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr"/>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W15" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2416,14 +2412,18 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26010522817050005414</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr"/>
+          <t>26010522846200005529</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -2440,12 +2440,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>347931</t>
+          <t>261646</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>90096</t>
+          <t>59150</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2455,17 +2455,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>DIEGO IVAN</t>
+          <t>VICTOR ALEXANDER</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>GODOY</t>
+          <t>QUINTANA</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>VELEZQUEZ</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6863853422</t>
+          <t>6624295211</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2486,17 +2486,17 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>27-01-2006</t>
+          <t>08-02-1988</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>DGODOY.I.827@GMAIL.COM</t>
+          <t>QUINTANAVICTOR@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>03-03-2026 05:04:50</t>
+          <t>11-10-2024 21:33:35</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2521,7 +2521,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>03-03-2026 05:08:27</t>
+          <t>04-03-2026 15:40:17</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2543,7 +2543,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26010522822770005455</t>
+          <t>26010522885580005673</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr"/>
@@ -2555,24 +2555,24 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Eduardo  Rivera Ramirez</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>347412</t>
+          <t>346585</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>89577</t>
+          <t>88750</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2582,17 +2582,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>DAYRANN</t>
+          <t>BETSY</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t xml:space="preserve">MORALES </t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t xml:space="preserve">QUIJADA </t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2602,10 +2602,14 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6242385160</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>6863893330</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>BRIONS 585</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -2613,32 +2617,32 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>14-11-2010</t>
+          <t>18-10-2008</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>NOTIENE2026@GMAIL.COM</t>
+          <t>BETSYMORALEES@GMAIL.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>02-03-2026 07:11:45</t>
+          <t>25-02-2026 19:18:01</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -2648,21 +2652,29 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>02-03-2026 07:13:01</t>
+          <t>02-03-2026 21:26:46</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr"/>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>02-03-2026 21:25:54</t>
+        </is>
+      </c>
       <c r="U17" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2670,11 +2682,19 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26010522781730005290</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr"/>
-      <c r="Z17" t="inlineStr"/>
+          <t>26010522820850005449</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>CHRISTIAN ERNESTO QUIÑONES GALVEZ</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>549</t>
@@ -2682,12 +2702,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>Javier Galaz Quintero</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2800,7 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T18" t="inlineStr"/>
@@ -2821,12 +2841,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>347399</t>
+          <t>347856</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>89564</t>
+          <t>90021</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2836,17 +2856,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>PEDRO</t>
+          <t xml:space="preserve">VICTOR MOISES </t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>SANTIAGO</t>
+          <t>LEON</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ORGANISTA</t>
+          <t>CIPRIAN</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2856,12 +2876,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>6864336712</t>
+          <t>6862806630</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>CERRO LORETO 524</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2871,22 +2891,22 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>07-10-1995</t>
+          <t>14-07-2006</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>PEDRO_SANTIAGO95@HOTMAIL.COM</t>
+          <t>ANNASTACIA841@GMAIL.COM</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>02-03-2026 06:08:22</t>
+          <t>02-03-2026 18:56:42</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -2896,7 +2916,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 LE</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -2906,17 +2926,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>05-03-2026 06:20:12</t>
+          <t>02-03-2026 18:59:57</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>02-03-2026 06:16:21</t>
+          <t>02-03-2026 18:59:18</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2936,19 +2956,11 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26010522908290005745</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>NORMA VERONICA MEJIA MACIAS</t>
-        </is>
-      </c>
+          <t>26010522814900005394</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr">
         <is>
           <t>549</t>
@@ -2968,12 +2980,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>348294</t>
+          <t>347866</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>90459</t>
+          <t>90031</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2983,17 +2995,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIRANDA </t>
+          <t>MARIA FERNANDA</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">CARRAZCO </t>
+          <t>IBARRA</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MEZA</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3003,12 +3015,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>6863919464</t>
+          <t>6864247889</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>DFB</t>
+          <t>XFGHSRT</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -3018,17 +3030,17 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>29-11-2006</t>
+          <t>24-01-2000</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>MIRANDACARRAZCO1@GMAIL.COM</t>
+          <t>FERNANDADEBI@GMAIL.COM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>03-03-2026 21:19:57</t>
+          <t>02-03-2026 19:23:59</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -3053,17 +3065,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>03-03-2026 21:22:26</t>
+          <t>02-03-2026 19:27:24</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>03-03-2026 21:21:59</t>
+          <t>02-03-2026 19:26:48</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -3083,7 +3095,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26010522862110005602</t>
+          <t>26010522816660005411</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr"/>
@@ -3197,7 +3209,7 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
@@ -3332,7 +3344,7 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T22" t="inlineStr"/>
@@ -3373,12 +3385,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>348106</t>
+          <t>347801</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>90271</t>
+          <t>89966</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3388,17 +3400,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>JULIO CESAR</t>
+          <t xml:space="preserve">JUAN IGNACIO </t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">SANCHEZ </t>
+          <t xml:space="preserve">PADILLA </t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>GARIBALDI</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3408,12 +3420,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>6971153889</t>
+          <t>6863540077</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>VALLE OJOS NEGROS 757</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3423,17 +3435,17 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>28-06-2000</t>
+          <t>18-05-2000</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>JULIOCSANCHEZGARI@GMAIL.COM</t>
+          <t>JUANIGNACIOPADILLAHERNANDEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>03-03-2026 16:04:08</t>
+          <t>02-03-2026 18:13:39</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -3458,17 +3470,17 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>03-03-2026 16:08:28</t>
+          <t>02-03-2026 18:26:08</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>03-03-2026 16:07:31</t>
+          <t>02-03-2026 18:23:34</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -3488,7 +3500,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>26010522845650005525</t>
+          <t>26010522811900005387</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr"/>
@@ -3500,24 +3512,24 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Eduardo  Rivera Ramirez</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>347801</t>
+          <t>347862</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>89966</t>
+          <t>90027</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3527,17 +3539,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">JUAN IGNACIO </t>
+          <t>DAVID ALEJANDRO</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">PADILLA </t>
+          <t>CIPRIAN</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>BELTRAN</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3547,12 +3559,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>6863540077</t>
+          <t>6863468966</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>VALLE OJOS NEGROS 757</t>
+          <t>CERRO LORETO 524</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3562,17 +3574,17 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>18-05-2000</t>
+          <t>26-10-1996</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>JUANIGNACIOPADILLAHERNANDEZ@GMAIL.COM</t>
+          <t>ALEXDUTY@GMAIL.COM</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>02-03-2026 18:13:39</t>
+          <t>02-03-2026 19:12:02</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3597,17 +3609,17 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>02-03-2026 18:26:08</t>
+          <t>02-03-2026 19:14:31</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>02-03-2026 18:23:34</t>
+          <t>02-03-2026 19:13:58</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3627,7 +3639,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>26010522811900005387</t>
+          <t>26010522815760005403</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr"/>
@@ -3639,24 +3651,24 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>Eduardo  Rivera Ramirez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>347862</t>
+          <t>347396</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>90027</t>
+          <t>89561</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3666,17 +3678,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>DAVID ALEJANDRO</t>
+          <t>ARELY</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>CIPRIAN</t>
+          <t xml:space="preserve">RAMOS </t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>BELTRAN</t>
+          <t>NUÑEZ</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3686,32 +3698,32 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>6863468966</t>
+          <t>6865305780</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>CERRO LORETO 524</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>26-10-1996</t>
+          <t>14-04-2000</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>ALEXDUTY@GMAIL.COM</t>
+          <t>ARELYRAMOS1960@GMAIL.COM</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>02-03-2026 19:12:02</t>
+          <t>02-03-2026 06:00:12</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3736,7 +3748,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>02-03-2026 19:14:31</t>
+          <t>04-03-2026 05:21:09</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3746,7 +3758,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>02-03-2026 19:13:58</t>
+          <t>03-03-2026 11:30:09</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3766,11 +3778,19 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>26010522815760005403</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr"/>
-      <c r="Z25" t="inlineStr"/>
+          <t>26010522864510005614</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>NORMA VERONICA MEJIA MACIAS</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>549</t>
@@ -3778,24 +3798,24 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Cristobal Lopez Miranda</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>347856</t>
+          <t>348326</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>90021</t>
+          <t>90491</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3805,17 +3825,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">VICTOR MOISES </t>
+          <t xml:space="preserve">KEYLA </t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>LEON</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CIPRIAN</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3825,47 +3845,43 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>6862806630</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>CERRO LORETO 524</t>
-        </is>
-      </c>
+          <t>6861631127</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>14-07-2006</t>
+          <t>23-11-2012</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>ANNASTACIA841@GMAIL.COM</t>
+          <t>NOTIENCORREO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>02-03-2026 18:56:42</t>
+          <t>04-03-2026 07:02:53</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -3875,29 +3891,21 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>02-03-2026 18:59:57</t>
+          <t>04-03-2026 07:05:18</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>02-03-2026 18:59:18</t>
-        </is>
-      </c>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3905,7 +3913,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>26010522814900005394</t>
+          <t>26010522873570005627</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr"/>
@@ -3917,24 +3925,24 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Javier Galaz Quintero</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>347866</t>
+          <t>348106</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>90031</t>
+          <t>90271</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3944,17 +3952,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>MARIA FERNANDA</t>
+          <t>JULIO CESAR</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>IBARRA</t>
+          <t xml:space="preserve">SANCHEZ </t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>GARIBALDI</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -3964,32 +3972,32 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>6864247889</t>
+          <t>6971153889</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>XFGHSRT</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>24-01-2000</t>
+          <t>28-06-2000</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>FERNANDADEBI@GMAIL.COM</t>
+          <t>JULIOCSANCHEZGARI@GMAIL.COM</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>02-03-2026 19:23:59</t>
+          <t>03-03-2026 16:04:08</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -4014,7 +4022,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>02-03-2026 19:27:24</t>
+          <t>03-03-2026 16:08:28</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -4024,7 +4032,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>02-03-2026 19:26:48</t>
+          <t>03-03-2026 16:07:31</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -4044,7 +4052,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>26010522816660005411</t>
+          <t>26010522845650005525</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr"/>
@@ -4068,12 +4076,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>347093</t>
+          <t>348250</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>89258</t>
+          <t>90415</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4083,17 +4091,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARTURO </t>
+          <t>FRIDA GABRIELA</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>HINOJOSA</t>
+          <t xml:space="preserve">NEVAREZ </t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>FIERRO</t>
+          <t>ARANGURE</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4103,47 +4111,47 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>6867221281</t>
+          <t>6863950637</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>DFB</t>
+          <t>FERMIN RIVERA 1501</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>28-02-1996</t>
+          <t>29-09-1999</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>AHINOJOS809@GMAIL.COM</t>
+          <t>FRIDARANGURE@GMAIL.COM</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>27-02-2026 20:53:44</t>
+          <t>03-03-2026 19:00:45</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -4153,29 +4161,21 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>03-03-2026 19:27:54</t>
+          <t>03-03-2026 19:45:30</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>03-03-2026 19:27:21</t>
-        </is>
-      </c>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4183,19 +4183,11 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>26010522858800005570</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>CHRISTIAN ERNESTO QUIÑONES GALVEZ</t>
-        </is>
-      </c>
+          <t>26010522859740005576</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr">
         <is>
           <t>549</t>
@@ -4215,12 +4207,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>347365</t>
+          <t>348267</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>89530</t>
+          <t>90432</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4230,17 +4222,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>ARJENNIS</t>
+          <t xml:space="preserve">ADOLFO ANGEL </t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>FIERRO</t>
+          <t xml:space="preserve">ALVARADO </t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>ORTEGA</t>
+          <t>ALVAREZ</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4250,39 +4242,47 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>6864599242</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+          <t>6381141056</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>GUIRNALDA 991</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>28-11-2002</t>
+          <t>02-08-1999</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>ARJENNIS.FIERRO28@GMAIL.COM</t>
+          <t>ALVARADOADOLFO07@GMAIL.COM</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>02-03-2026 00:25:45</t>
+          <t>03-03-2026 19:26:50</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
@@ -4292,21 +4292,29 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>04-03-2026 05:42:50</t>
+          <t>03-03-2026 19:32:17</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr"/>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>03-03-2026 19:31:29</t>
+        </is>
+      </c>
       <c r="U29" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr"/>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W29" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4314,14 +4322,10 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>26010522865080005623</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26010522859120005572</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr"/>
       <c r="Z29" t="inlineStr"/>
       <c r="AA29" t="inlineStr">
         <is>
@@ -4342,12 +4346,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>348267</t>
+          <t>348294</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>90432</t>
+          <t>90459</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4357,17 +4361,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADOLFO ANGEL </t>
+          <t xml:space="preserve">MIRANDA </t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALVARADO </t>
+          <t xml:space="preserve">CARRAZCO </t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>ALVAREZ</t>
+          <t>MEZA</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4377,32 +4381,32 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>6381141056</t>
+          <t>6863919464</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>GUIRNALDA 991</t>
+          <t>DFB</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>02-08-1999</t>
+          <t>29-11-2006</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>ALVARADOADOLFO07@GMAIL.COM</t>
+          <t>MIRANDACARRAZCO1@GMAIL.COM</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>03-03-2026 19:26:50</t>
+          <t>03-03-2026 21:19:57</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -4427,17 +4431,17 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>03-03-2026 19:32:17</t>
+          <t>03-03-2026 21:22:26</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>03-03-2026 19:31:29</t>
+          <t>03-03-2026 21:21:59</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -4447,7 +4451,7 @@
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
@@ -4457,7 +4461,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>26010522859120005572</t>
+          <t>26010522862110005602</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr"/>
@@ -4481,12 +4485,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>348250</t>
+          <t>348803</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>90415</t>
+          <t>90968</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4496,17 +4500,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>FRIDA GABRIELA</t>
+          <t>JESUS ALBERTO</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">NEVAREZ </t>
+          <t>MENDIVIL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>ARANGURE</t>
+          <t>VALENZUELA</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4516,47 +4520,47 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>6863950637</t>
+          <t>6442612015</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>FERMIN RIVERA 1501</t>
+          <t>FSFDG</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>29-09-1999</t>
+          <t>15-11-1997</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>FRIDARANGURE@GMAIL.COM</t>
+          <t>JAMV.MVJA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>03-03-2026 19:00:45</t>
+          <t>05-03-2026 19:26:51</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -4566,21 +4570,29 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>03-03-2026 19:45:30</t>
+          <t>05-03-2026 19:33:05</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T31" t="inlineStr"/>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>05-03-2026 19:32:23</t>
+        </is>
+      </c>
       <c r="U31" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V31" t="inlineStr"/>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W31" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4588,7 +4600,7 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>26010522859740005576</t>
+          <t>26010522929680005806</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr"/>
@@ -4600,24 +4612,24 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Eduardo  Rivera Ramirez</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>348740</t>
+          <t>348807</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>90905</t>
+          <t>90972</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4627,17 +4639,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>DIANA ELIZABETH</t>
+          <t>ITATY ARLETT</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>FERNANDEZ</t>
+          <t>VALDEZ</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>ROBLES</t>
+          <t>ANGUIS</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4647,12 +4659,12 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>6861377114</t>
+          <t>6862318833</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>FDGH</t>
+          <t>DZFG</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4662,17 +4674,17 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>14-01-1976</t>
+          <t>24-08-2000</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>DIANAFERNANDEZ1401@GMAIL.COM</t>
+          <t>NOTELECTRCORR@GMAIL.COM</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>05-03-2026 16:13:04</t>
+          <t>05-03-2026 19:35:31</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -4697,17 +4709,17 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>05-03-2026 16:17:39</t>
+          <t>05-03-2026 19:38:30</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>05-04-2026 23:59:59</t>
+          <t>04-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>05-03-2026 16:17:02</t>
+          <t>05-03-2026 19:37:55</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -4727,7 +4739,7 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>26010522920680005786</t>
+          <t>26010522929930005807</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr"/>
@@ -4739,24 +4751,24 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Eduardo  Rivera Ramirez</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>348789</t>
+          <t>348740</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>90954</t>
+          <t>90905</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4766,17 +4778,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">DULCE KARINA </t>
+          <t>DIANA ELIZABETH</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">SANDOVAL </t>
+          <t>FERNANDEZ</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>ROBLES</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4786,43 +4798,47 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>6862476066</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>6861377114</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>FDGH</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>03-07-1995</t>
+          <t>14-01-1976</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>KARISAN030795@GMAIL.COM</t>
+          <t>DIANAFERNANDEZ1401@GMAIL.COM</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>05-03-2026 18:11:01</t>
+          <t>05-03-2026 16:13:04</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
@@ -4832,21 +4848,29 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>05-03-2026 18:23:48</t>
+          <t>05-03-2026 16:17:39</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>05-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr"/>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>05-03-2026 16:17:02</t>
+        </is>
+      </c>
       <c r="U33" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V33" t="inlineStr"/>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W33" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4854,7 +4878,7 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>26010522926990005795</t>
+          <t>26010522920680005786</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr"/>
@@ -4878,12 +4902,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>348326</t>
+          <t>348789</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>90491</t>
+          <t>90954</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4893,17 +4917,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">KEYLA </t>
+          <t xml:space="preserve">DULCE KARINA </t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t xml:space="preserve">SANDOVAL </t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4913,7 +4937,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>6861631127</t>
+          <t>6862476066</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4924,17 +4948,17 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>23-11-2012</t>
+          <t>03-07-1995</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>NOTIENCORREO@GMAIL.COM</t>
+          <t>KARISAN030795@GMAIL.COM</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>04-03-2026 07:02:53</t>
+          <t>05-03-2026 18:11:01</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -4959,7 +4983,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>04-03-2026 07:05:18</t>
+          <t>05-03-2026 18:23:48</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4970,7 +4994,7 @@
       <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V34" t="inlineStr"/>
@@ -4981,7 +5005,7 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>26010522873570005627</t>
+          <t>26010522926990005795</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr"/>
@@ -4993,24 +5017,24 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>Javier Galaz Quintero</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>348803</t>
+          <t>349162</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>90968</t>
+          <t>91327</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5020,17 +5044,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>JESUS ALBERTO</t>
+          <t xml:space="preserve">AZUCENA </t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>MENDIVIL</t>
+          <t xml:space="preserve">GARZA </t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>VALENZUELA</t>
+          <t>CAZARES</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -5040,47 +5064,43 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>6442612015</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>FSFDG</t>
-        </is>
-      </c>
+          <t>6867360863</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>15-11-1997</t>
+          <t>16-08-2001</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>JAMV.MVJA@GMAIL.COM</t>
+          <t>GARZACAZARES@GMAIL.COM</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>05-03-2026 19:26:51</t>
+          <t>07-03-2026 14:50:46</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
@@ -5090,29 +5110,21 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>05-03-2026 19:33:05</t>
+          <t>07-03-2026 15:07:14</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>05-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>05-03-2026 19:32:23</t>
-        </is>
-      </c>
+          <t>06-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr"/>
       <c r="U35" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V35" t="inlineStr"/>
       <c r="W35" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5120,7 +5132,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>26010522929680005806</t>
+          <t>26010522976130005950</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr"/>
@@ -5144,12 +5156,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>348807</t>
+          <t>347870</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>90972</t>
+          <t>90035</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5159,17 +5171,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>ITATY ARLETT</t>
+          <t>FRANCISCO JOSUE</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>VALDEZ</t>
+          <t>FERNANDEZ</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>ANGUIS</t>
+          <t>BECERRA</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5179,79 +5191,67 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>6862318833</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>DZFG</t>
-        </is>
-      </c>
+          <t>6643747758</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>24-08-2000</t>
+          <t>12-02-1997</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>NOTELECTRCORR@GMAIL.COM</t>
+          <t>JOSUE.FERNANDEZ@UABC.EDU.MX</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>05-03-2026 19:35:31</t>
+          <t>02-03-2026 19:32:25</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>05-03-2026 19:38:30</t>
+          <t>02-03-2026 19:33:13</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>05-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>05-03-2026 19:37:55</t>
-        </is>
-      </c>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V36" t="inlineStr"/>
       <c r="W36" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5259,14 +5259,14 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>26010522929930005807</t>
+          <t>26010522817050005414</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr"/>
       <c r="Z36" t="inlineStr"/>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
@@ -5275,6 +5275,260 @@
         </is>
       </c>
       <c r="AC36" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>347931</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>90096</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>DIEGO IVAN</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>GODOY</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>VELEZQUEZ</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>6863853422</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>27-01-2006</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>DGODOY.I.827@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>03-03-2026 05:04:50</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>03-03-2026 05:08:27</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr"/>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>26010522822770005455</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr"/>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>348588</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>90753</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>IRAN ISRAEL</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CARRASCO </t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>ALMARAZ</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>6864154907</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>18-11-1998</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>YAYEL686@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>04-03-2026 19:15:07</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>06-03-2026 19:29:02</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr"/>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>26010522960500005899</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr"/>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
         <is>
           <t>sin rutina</t>
         </is>
